--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -186,6 +186,9 @@
   </x:si>
   <x:si>
     <x:t>s001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTIAL</x:t>
   </x:si>
   <x:si>
     <x:t>(MISSING - not captured)</x:t>
@@ -233,7 +236,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -243,6 +246,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -275,7 +283,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -291,8 +299,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -310,6 +321,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1062,10 +1077,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>52896</x:v>
+        <x:v>51749</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1118,10 +1133,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>52896</x:v>
+        <x:v>51749</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,10 +1189,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>52896</x:v>
+        <x:v>51749</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1230,10 +1245,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>52896</x:v>
+        <x:v>51749</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1277,22 +1292,22 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4004</x:v>
+        <x:v>51749</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>52896</x:v>
-      </x:c>
-      <x:c r="R6" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>4005</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1327,7 +1342,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1347,8 +1362,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>57</x:v>
+      <x:c r="R7" s="4" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1389,22 +1404,22 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>52896</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4004</x:v>
-      </x:c>
-      <x:c r="R8" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>51749</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1412,7 +1427,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1439,10 +1454,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>45</x:v>
@@ -1454,13 +1469,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>52896</x:v>
-      </x:c>
-      <x:c r="R9" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>51749</x:v>
+      </x:c>
+      <x:c r="R9" s="5" t="s">
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1468,7 +1483,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>17</x:v>
@@ -1495,10 +1510,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
         <x:v>44</x:v>
@@ -1510,13 +1525,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>52896</x:v>
+        <x:v>51749</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4004</x:v>
-      </x:c>
-      <x:c r="R10" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>4005</x:v>
+      </x:c>
+      <x:c r="R10" s="5" t="s">
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1524,7 +1539,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>17</x:v>
@@ -1566,13 +1581,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>4004</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>52896</x:v>
-      </x:c>
-      <x:c r="R11" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>51749</x:v>
+      </x:c>
+      <x:c r="R11" s="5" t="s">
+        <x:v>62</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,10 +1077,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>51749</x:v>
+        <x:v>55496</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1133,10 +1133,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>51749</x:v>
+        <x:v>55496</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,10 +1189,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>51749</x:v>
+        <x:v>55496</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1245,10 +1245,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>51749</x:v>
+        <x:v>55496</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1301,10 +1301,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>51749</x:v>
+        <x:v>55496</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1413,10 +1413,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>51749</x:v>
+        <x:v>55496</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1469,10 +1469,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>51749</x:v>
+        <x:v>55496</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,10 +1525,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>51749</x:v>
+        <x:v>55496</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R10" s="5" t="s">
         <x:v>62</x:v>
@@ -1581,10 +1581,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>51749</x:v>
+        <x:v>55496</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,10 +1077,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55496</x:v>
+        <x:v>52522</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1133,10 +1133,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55496</x:v>
+        <x:v>52522</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,10 +1189,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55496</x:v>
+        <x:v>52522</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1245,10 +1245,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55496</x:v>
+        <x:v>52522</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1301,10 +1301,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>55496</x:v>
+        <x:v>52522</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1413,10 +1413,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>55496</x:v>
+        <x:v>52522</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1469,10 +1469,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55496</x:v>
+        <x:v>52522</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,10 +1525,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>55496</x:v>
+        <x:v>52522</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="R10" s="5" t="s">
         <x:v>62</x:v>
@@ -1581,10 +1581,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>4000</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>55496</x:v>
+        <x:v>52522</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,10 +1077,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>52522</x:v>
+        <x:v>59458</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1133,10 +1133,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>52522</x:v>
+        <x:v>59458</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,10 +1189,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>52522</x:v>
+        <x:v>59458</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1245,10 +1245,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>52522</x:v>
+        <x:v>59458</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1301,10 +1301,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>52522</x:v>
+        <x:v>59458</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>56</x:v>
@@ -1413,10 +1413,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>52522</x:v>
+        <x:v>59458</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1469,10 +1469,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>52522</x:v>
+        <x:v>59458</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,10 +1525,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>52522</x:v>
+        <x:v>59458</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R10" s="5" t="s">
         <x:v>62</x:v>
@@ -1581,10 +1581,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>4005</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>52522</x:v>
+        <x:v>59458</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>59458</x:v>
+        <x:v>51931</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>59458</x:v>
+        <x:v>51931</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>59458</x:v>
+        <x:v>51931</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>59458</x:v>
+        <x:v>51931</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>59458</x:v>
+        <x:v>51931</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>59458</x:v>
+        <x:v>51931</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>59458</x:v>
+        <x:v>51931</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>59458</x:v>
+        <x:v>51931</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>59458</x:v>
+        <x:v>51931</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>51931</x:v>
+        <x:v>62625</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>51931</x:v>
+        <x:v>62625</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>51931</x:v>
+        <x:v>62625</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>51931</x:v>
+        <x:v>62625</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>51931</x:v>
+        <x:v>62625</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>51931</x:v>
+        <x:v>62625</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>51931</x:v>
+        <x:v>62625</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>51931</x:v>
+        <x:v>62625</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>51931</x:v>
+        <x:v>62625</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>62625</x:v>
+        <x:v>65207</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>62625</x:v>
+        <x:v>65207</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>62625</x:v>
+        <x:v>65207</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>62625</x:v>
+        <x:v>65207</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>62625</x:v>
+        <x:v>65207</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>62625</x:v>
+        <x:v>65207</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>62625</x:v>
+        <x:v>65207</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>62625</x:v>
+        <x:v>65207</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>62625</x:v>
+        <x:v>65207</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>65207</x:v>
+        <x:v>49944</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>65207</x:v>
+        <x:v>49944</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>65207</x:v>
+        <x:v>49944</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>65207</x:v>
+        <x:v>49944</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>65207</x:v>
+        <x:v>49944</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>65207</x:v>
+        <x:v>49944</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>65207</x:v>
+        <x:v>49944</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>65207</x:v>
+        <x:v>49944</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>65207</x:v>
+        <x:v>49944</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49944</x:v>
+        <x:v>49185</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49944</x:v>
+        <x:v>49185</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49944</x:v>
+        <x:v>49185</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>49944</x:v>
+        <x:v>49185</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49944</x:v>
+        <x:v>49185</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49944</x:v>
+        <x:v>49185</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>49944</x:v>
+        <x:v>49185</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>49944</x:v>
+        <x:v>49185</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>49944</x:v>
+        <x:v>49185</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49185</x:v>
+        <x:v>54249</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49185</x:v>
+        <x:v>54249</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49185</x:v>
+        <x:v>54249</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>49185</x:v>
+        <x:v>54249</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49185</x:v>
+        <x:v>54249</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49185</x:v>
+        <x:v>54249</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>49185</x:v>
+        <x:v>54249</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>49185</x:v>
+        <x:v>54249</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>49185</x:v>
+        <x:v>54249</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54249</x:v>
+        <x:v>56545</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54249</x:v>
+        <x:v>56545</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54249</x:v>
+        <x:v>56545</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54249</x:v>
+        <x:v>56545</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>54249</x:v>
+        <x:v>56545</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>54249</x:v>
+        <x:v>56545</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>54249</x:v>
+        <x:v>56545</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>54249</x:v>
+        <x:v>56545</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>54249</x:v>
+        <x:v>56545</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>56545</x:v>
+        <x:v>57277</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>56545</x:v>
+        <x:v>57277</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>56545</x:v>
+        <x:v>57277</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>56545</x:v>
+        <x:v>57277</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>56545</x:v>
+        <x:v>57277</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>56545</x:v>
+        <x:v>57277</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>56545</x:v>
+        <x:v>57277</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>56545</x:v>
+        <x:v>57277</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>56545</x:v>
+        <x:v>57277</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>
